--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -903,7 +903,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -919,7 +919,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>as-ext-organization-pricing-model</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -957,7 +957,7 @@
     <t>as-ext-organization-closing-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -979,7 +979,7 @@
     <t>as-ext-organization-budget-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -998,7 +998,7 @@
     <t>as-ext-organization-authorization-deadline</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1790,7 +1790,7 @@
     <t>as-ext-organization-types</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Organization.type:organizationType.coding</t>
@@ -2097,7 +2097,7 @@
     <t>Le type d’établissement détermine si c'est un établissement principal ou secondaire.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>EntiteGeographique.typeEtablissement</t>
@@ -2380,7 +2380,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2444,7 +2444,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2606,7 +2606,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-1}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2648,7 +2648,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
